--- a/slw/3907BS_BOM_Raw.xlsx
+++ b/slw/3907BS_BOM_Raw.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hkustconnect-my.sharepoint.com/personal/tkzhang_connect_ust_hk/Documents/26 Spring/MECH3907/2026-MECH3907-Gp7-TTB-shooter/slw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="10_ncr:80_{26C905CC-0604-498D-9F83-ECB39E4D846C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD07CFF1-A667-4B1E-BFAF-2851A126E582}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="10_ncr:80_{26C905CC-0604-498D-9F83-ECB39E4D846C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B9D3A45-C7CC-4F60-9B6C-E9C5D9E7A5D5}"/>
   <bookViews>
-    <workbookView xWindow="4905" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{A18A69EC-BAB9-4A80-8D34-14BD25FB6736}"/>
+    <workbookView xWindow="-96" yWindow="6480" windowWidth="23136" windowHeight="6576" xr2:uid="{A18A69EC-BAB9-4A80-8D34-14BD25FB6736}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -812,17 +812,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{238E7827-F4F4-44CD-BBF2-412081C603FC}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:D56"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.875" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.88671875" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -836,7 +835,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>66</v>
       </c>
@@ -848,7 +847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -860,7 +859,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -872,7 +871,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -884,7 +883,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -896,7 +895,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -908,7 +907,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>68</v>
       </c>
@@ -920,7 +919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
@@ -932,7 +931,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
@@ -944,7 +943,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
@@ -956,7 +955,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -968,7 +967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>26</v>
       </c>
@@ -980,7 +979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>106</v>
       </c>
@@ -992,7 +991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>30</v>
       </c>
@@ -1004,7 +1003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>32</v>
       </c>
@@ -1016,7 +1015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>34</v>
       </c>
@@ -1028,7 +1027,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>36</v>
       </c>
@@ -1040,7 +1039,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>38</v>
       </c>
@@ -1052,7 +1051,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>40</v>
       </c>
@@ -1064,7 +1063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>42</v>
       </c>
@@ -1076,7 +1075,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>44</v>
       </c>
@@ -1088,7 +1087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>46</v>
       </c>
@@ -1100,7 +1099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>48</v>
       </c>
@@ -1112,7 +1111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>50</v>
       </c>
@@ -1124,7 +1123,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>52</v>
       </c>
@@ -1136,7 +1135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="33.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="35.4" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>54</v>
       </c>
@@ -1148,7 +1147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>56</v>
       </c>
@@ -1160,7 +1159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>58</v>
       </c>
@@ -1172,7 +1171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>60</v>
       </c>
@@ -1184,7 +1183,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>62</v>
       </c>
@@ -1196,7 +1195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>108</v>
       </c>
@@ -1208,7 +1207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>4</v>
       </c>
@@ -1220,7 +1219,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>16</v>
       </c>
@@ -1232,7 +1231,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>70</v>
       </c>
@@ -1244,7 +1243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>72</v>
       </c>
@@ -1258,7 +1257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>28</v>
       </c>
@@ -1270,7 +1269,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>76</v>
       </c>
@@ -1282,7 +1281,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>78</v>
       </c>
@@ -1294,7 +1293,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>80</v>
       </c>
@@ -1306,7 +1305,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>82</v>
       </c>
@@ -1318,7 +1317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>84</v>
       </c>
@@ -1330,7 +1329,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>85</v>
       </c>
@@ -1342,7 +1341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>87</v>
       </c>
@@ -1354,7 +1353,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>89</v>
       </c>
@@ -1366,7 +1365,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>90</v>
       </c>
@@ -1378,7 +1377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>92</v>
       </c>
@@ -1390,7 +1389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>94</v>
       </c>
@@ -1402,7 +1401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>96</v>
       </c>
@@ -1414,7 +1413,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>98</v>
       </c>
@@ -1426,7 +1425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>100</v>
       </c>
@@ -1438,7 +1437,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>102</v>
       </c>
@@ -1450,7 +1449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>104</v>
       </c>
@@ -1462,7 +1461,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>64</v>
       </c>
@@ -1474,7 +1473,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>74</v>
       </c>
@@ -1486,7 +1485,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>110</v>
       </c>
@@ -1500,11 +1499,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:D56" xr:uid="{238E7827-F4F4-44CD-BBF2-412081C603FC}">
-    <filterColumn colId="1">
-      <customFilters>
-        <customFilter val="*LSC*"/>
-      </customFilters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D55">
       <sortCondition ref="B1:B56"/>
     </sortState>
